--- a/PlayGround/Verification Freq_Metrics/FreqMetrics_Reference_Auswertung.xlsx
+++ b/PlayGround/Verification Freq_Metrics/FreqMetrics_Reference_Auswertung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Flo\Datenbox9000\ZHAW\Faecher\BA\Control-Optimizer\PlayGround\Verification Freq_Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98F84E77-E5F2-40B3-A5D0-90DB506776CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE325E1-292E-4FD5-B65D-09971E384068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,12 +126,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -148,7 +154,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -571,7 +577,7 @@
       <c r="M3">
         <v>5.36824300454421</v>
       </c>
-      <c r="O3" s="1">
+      <c r="O3">
         <v>-102.639292771933</v>
       </c>
       <c r="P3">
@@ -584,15 +590,15 @@
         <v>1.0460998695055801</v>
       </c>
       <c r="T3" t="e">
-        <f>K3-O3</f>
+        <f t="shared" ref="T3:T34" si="0">K3-O3</f>
         <v>#VALUE!</v>
       </c>
       <c r="U3">
-        <f>J3-P3</f>
+        <f t="shared" ref="U3:U34" si="1">J3-P3</f>
         <v>-3.8155299182420777E-3</v>
       </c>
       <c r="V3">
-        <f>L3-R3</f>
+        <f t="shared" ref="V3:V34" si="2">L3-R3</f>
         <v>-5.2709691960028948E-6</v>
       </c>
       <c r="W3">
@@ -640,7 +646,7 @@
       <c r="M4">
         <v>5.4621338365697172</v>
       </c>
-      <c r="O4" s="1">
+      <c r="O4">
         <v>-103.907149061271</v>
       </c>
       <c r="P4">
@@ -653,19 +659,19 @@
         <v>1.04650419156045</v>
       </c>
       <c r="T4" t="e">
-        <f>K4-O4</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U4">
-        <f>J4-P4</f>
+        <f t="shared" si="1"/>
         <v>-4.6401967191513904E-3</v>
       </c>
       <c r="V4">
-        <f>L4-R4</f>
+        <f t="shared" si="2"/>
         <v>-9.076907871108375E-6</v>
       </c>
       <c r="W4">
-        <f t="shared" ref="W4:W62" si="0">M4-Q4</f>
+        <f t="shared" ref="W4:W62" si="3">M4-Q4</f>
         <v>2.1744893320869707E-3</v>
       </c>
     </row>
@@ -709,7 +715,7 @@
       <c r="M5">
         <v>5.4438749989384201</v>
       </c>
-      <c r="O5" s="1">
+      <c r="O5">
         <v>-104.656462621618</v>
       </c>
       <c r="P5">
@@ -722,19 +728,19 @@
         <v>1.04638251337882</v>
       </c>
       <c r="T5" t="e">
-        <f>K5-O5</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U5">
-        <f>J5-P5</f>
+        <f t="shared" si="1"/>
         <v>-4.704792800538371E-3</v>
       </c>
       <c r="V5">
-        <f>L5-R5</f>
+        <f t="shared" si="2"/>
         <v>-2.3267259401382745E-6</v>
       </c>
       <c r="W5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.2620923771698997E-3</v>
       </c>
     </row>
@@ -778,7 +784,7 @@
       <c r="M6">
         <v>5.4378589841906573</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O6">
         <v>-105.339816054095</v>
       </c>
       <c r="P6">
@@ -791,19 +797,19 @@
         <v>1.0462979445448399</v>
       </c>
       <c r="T6" t="e">
-        <f>K6-O6</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U6">
-        <f>J6-P6</f>
+        <f t="shared" si="1"/>
         <v>-4.6372187895684647E-3</v>
       </c>
       <c r="V6">
-        <f>L6-R6</f>
+        <f t="shared" si="2"/>
         <v>-1.025640818941298E-6</v>
       </c>
       <c r="W6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.2764981778875537E-3</v>
       </c>
     </row>
@@ -860,19 +866,19 @@
         <v>1.4943253696655501</v>
       </c>
       <c r="T7" t="e">
-        <f>K7-O7</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U7">
-        <f>J7-P7</f>
+        <f t="shared" si="1"/>
         <v>-7.9351920436536716E-3</v>
       </c>
       <c r="V7">
-        <f>L7-R7</f>
+        <f t="shared" si="2"/>
         <v>-2.5120346128115756E-5</v>
       </c>
       <c r="W7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.6209992455751276E-3</v>
       </c>
     </row>
@@ -929,19 +935,19 @@
         <v>1.4938882905285999</v>
       </c>
       <c r="T8" t="e">
-        <f>K8-O8</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U8">
-        <f>J8-P8</f>
+        <f t="shared" si="1"/>
         <v>-4.8697559834991466E-3</v>
       </c>
       <c r="V8">
-        <f>L8-R8</f>
+        <f t="shared" si="2"/>
         <v>-5.0504861869704598E-4</v>
       </c>
       <c r="W8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.076488314471824E-3</v>
       </c>
     </row>
@@ -998,19 +1004,19 @@
         <v>1.4922282245001199</v>
       </c>
       <c r="T9" t="e">
-        <f>K9-O9</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U9">
-        <f>J9-P9</f>
+        <f t="shared" si="1"/>
         <v>-8.17201155121694E-3</v>
       </c>
       <c r="V9">
-        <f>L9-R9</f>
+        <f t="shared" si="2"/>
         <v>-4.8372036238752969E-6</v>
       </c>
       <c r="W9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.8035984974771324E-3</v>
       </c>
     </row>
@@ -1067,19 +1073,19 @@
         <v>1.4917068412135901</v>
       </c>
       <c r="T10" t="e">
-        <f>K10-O10</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U10">
-        <f>J10-P10</f>
+        <f t="shared" si="1"/>
         <v>-4.1038180236441235E-3</v>
       </c>
       <c r="V10">
-        <f>L10-R10</f>
+        <f t="shared" si="2"/>
         <v>-5.5017124258704975E-4</v>
       </c>
       <c r="W10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>9.0803438070707898E-4</v>
       </c>
     </row>
@@ -1136,19 +1142,19 @@
         <v>1.21848462467986</v>
       </c>
       <c r="T11" t="e">
-        <f>K11-O11</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U11">
-        <f>J11-P11</f>
+        <f t="shared" si="1"/>
         <v>-1.8375097153722209E-3</v>
       </c>
       <c r="V11">
-        <f>L11-R11</f>
+        <f t="shared" si="2"/>
         <v>-6.1711556109900201E-5</v>
       </c>
       <c r="W11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4.9597773176834892E-4</v>
       </c>
     </row>
@@ -1205,19 +1211,19 @@
         <v>1.21795611193352</v>
       </c>
       <c r="T12" t="e">
-        <f>K12-O12</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U12">
-        <f>J12-P12</f>
+        <f t="shared" si="1"/>
         <v>-2.2970537499844568E-4</v>
       </c>
       <c r="V12">
-        <f>L12-R12</f>
+        <f t="shared" si="2"/>
         <v>-1.1316289098695087E-4</v>
       </c>
       <c r="W12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.2815209344257994E-5</v>
       </c>
     </row>
@@ -1274,19 +1280,19 @@
         <v>1.21830742747593</v>
       </c>
       <c r="T13" t="e">
-        <f>K13-O13</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U13">
-        <f>J13-P13</f>
+        <f t="shared" si="1"/>
         <v>-4.9337841227981016E-3</v>
       </c>
       <c r="V13">
-        <f>L13-R13</f>
+        <f t="shared" si="2"/>
         <v>-4.9347566279944743E-6</v>
       </c>
       <c r="W13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.3690108214623464E-3</v>
       </c>
     </row>
@@ -1343,19 +1349,19 @@
         <v>1.2183615128587</v>
       </c>
       <c r="T14" t="e">
-        <f>K14-O14</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U14">
-        <f>J14-P14</f>
+        <f t="shared" si="1"/>
         <v>-6.6921571247036127E-3</v>
       </c>
       <c r="V14">
-        <f>L14-R14</f>
+        <f t="shared" si="2"/>
         <v>-1.1149055034964661E-5</v>
       </c>
       <c r="W14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.8795961850806009E-3</v>
       </c>
     </row>
@@ -1412,19 +1418,19 @@
         <v>1.13554733662247</v>
       </c>
       <c r="T15" t="e">
-        <f>K15-O15</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U15">
-        <f>J15-P15</f>
+        <f t="shared" si="1"/>
         <v>-1.873006985590564E-3</v>
       </c>
       <c r="V15">
-        <f>L15-R15</f>
+        <f t="shared" si="2"/>
         <v>-5.5535393082895013E-5</v>
       </c>
       <c r="W15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.853242710469388E-4</v>
       </c>
     </row>
@@ -1481,19 +1487,19 @@
         <v>1.13595623378808</v>
       </c>
       <c r="T16" t="e">
-        <f>K16-O16</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U16">
-        <f>J16-P16</f>
+        <f t="shared" si="1"/>
         <v>-4.186601122867728E-3</v>
       </c>
       <c r="V16">
-        <f>L16-R16</f>
+        <f t="shared" si="2"/>
         <v>-1.3803476711871099E-5</v>
       </c>
       <c r="W16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.7124952835665397E-3</v>
       </c>
     </row>
@@ -1550,19 +1556,19 @@
         <v>1.1362854928802699</v>
       </c>
       <c r="T17" t="e">
-        <f>K17-O17</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U17">
-        <f>J17-P17</f>
+        <f t="shared" si="1"/>
         <v>-5.0428518513996323E-3</v>
       </c>
       <c r="V17">
-        <f>L17-R17</f>
+        <f t="shared" si="2"/>
         <v>-5.2092629031941229E-5</v>
       </c>
       <c r="W17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.1007740099543426E-3</v>
       </c>
     </row>
@@ -1619,19 +1625,19 @@
         <v>1.13534769477794</v>
       </c>
       <c r="T18" t="e">
-        <f>K18-O18</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U18">
-        <f>J18-P18</f>
+        <f t="shared" si="1"/>
         <v>-2.9941577903116467E-3</v>
       </c>
       <c r="V18">
-        <f>L18-R18</f>
+        <f t="shared" si="2"/>
         <v>2.2862676107848756E-7</v>
       </c>
       <c r="W18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.2897197981365238E-3</v>
       </c>
     </row>
@@ -1688,19 +1694,19 @@
         <v>1.0961517577086199</v>
       </c>
       <c r="T19" t="e">
-        <f>K19-O19</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U19">
-        <f>J19-P19</f>
+        <f t="shared" si="1"/>
         <v>-2.4021237835825104E-3</v>
       </c>
       <c r="V19">
-        <f>L19-R19</f>
+        <f t="shared" si="2"/>
         <v>-5.539797292009041E-6</v>
       </c>
       <c r="W19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.5479205893607073E-3</v>
       </c>
     </row>
@@ -1757,19 +1763,19 @@
         <v>1.09702003020126</v>
       </c>
       <c r="T20" t="e">
-        <f>K20-O20</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U20">
-        <f>J20-P20</f>
+        <f t="shared" si="1"/>
         <v>-2.4246757858605861E-3</v>
       </c>
       <c r="V20">
-        <f>L20-R20</f>
+        <f t="shared" si="2"/>
         <v>-5.2356769431050054E-6</v>
       </c>
       <c r="W20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.5604778860636159E-3</v>
       </c>
     </row>
@@ -1826,19 +1832,19 @@
         <v>1.09642638636953</v>
       </c>
       <c r="T21" t="e">
-        <f>K21-O21</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U21">
-        <f>J21-P21</f>
+        <f t="shared" si="1"/>
         <v>-2.9408267638757479E-3</v>
       </c>
       <c r="V21">
-        <f>L21-R21</f>
+        <f t="shared" si="2"/>
         <v>-3.4375463054070465E-5</v>
       </c>
       <c r="W21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.0490127091283838E-3</v>
       </c>
     </row>
@@ -1895,19 +1901,19 @@
         <v>1.0964394750330999</v>
       </c>
       <c r="T22" t="e">
-        <f>K22-O22</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U22">
-        <f>J22-P22</f>
+        <f t="shared" si="1"/>
         <v>-2.8661882125362581E-3</v>
       </c>
       <c r="V22">
-        <f>L22-R22</f>
+        <f t="shared" si="2"/>
         <v>-2.9063159370901204E-5</v>
       </c>
       <c r="W22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.0667610299280881E-3</v>
       </c>
     </row>
@@ -1964,19 +1970,19 @@
         <v>1.0734917977848599</v>
       </c>
       <c r="T23" t="e">
-        <f>K23-O23</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U23">
-        <f>J23-P23</f>
+        <f t="shared" si="1"/>
         <v>-1.3577672835509702E-3</v>
       </c>
       <c r="V23">
-        <f>L23-R23</f>
+        <f t="shared" si="2"/>
         <v>-2.0618447212017443E-5</v>
       </c>
       <c r="W23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.7368760682430207E-3</v>
       </c>
     </row>
@@ -2033,19 +2039,19 @@
         <v>1.0733080550019001</v>
       </c>
       <c r="T24" t="e">
-        <f>K24-O24</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U24">
-        <f>J24-P24</f>
+        <f t="shared" si="1"/>
         <v>-1.3290023970853326E-3</v>
       </c>
       <c r="V24">
-        <f>L24-R24</f>
+        <f t="shared" si="2"/>
         <v>-5.5971920209785253E-7</v>
       </c>
       <c r="W24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.9777211659262051E-3</v>
       </c>
     </row>
@@ -2102,19 +2108,19 @@
         <v>1.0731218568508001</v>
       </c>
       <c r="T25" t="e">
-        <f>K25-O25</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U25">
-        <f>J25-P25</f>
+        <f t="shared" si="1"/>
         <v>-1.1158922514340475E-3</v>
       </c>
       <c r="V25">
-        <f>L25-R25</f>
+        <f t="shared" si="2"/>
         <v>-1.4814907605131822E-5</v>
       </c>
       <c r="W25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.9903800315406173E-3</v>
       </c>
     </row>
@@ -2171,19 +2177,19 @@
         <v>1.0735420036291601</v>
       </c>
       <c r="T26" t="e">
-        <f>K26-O26</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U26">
-        <f>J26-P26</f>
+        <f t="shared" si="1"/>
         <v>-5.9679762036068951E-4</v>
       </c>
       <c r="V26">
-        <f>L26-R26</f>
+        <f t="shared" si="2"/>
         <v>-1.4621069604148218E-5</v>
       </c>
       <c r="W26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.0142782996265254E-3</v>
       </c>
     </row>
@@ -2240,19 +2246,19 @@
         <v>1.0579867853409199</v>
       </c>
       <c r="T27" t="e">
-        <f>K27-O27</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U27">
-        <f>J27-P27</f>
+        <f t="shared" si="1"/>
         <v>1.9232683284542418E-4</v>
       </c>
       <c r="V27">
-        <f>L27-R27</f>
+        <f t="shared" si="2"/>
         <v>-1.1790244473841582E-5</v>
       </c>
       <c r="W27">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.8933853208649154E-3</v>
       </c>
     </row>
@@ -2309,19 +2315,19 @@
         <v>1.05770352776078</v>
       </c>
       <c r="T28" t="e">
-        <f>K28-O28</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U28">
-        <f>J28-P28</f>
+        <f t="shared" si="1"/>
         <v>4.03108336328728E-4</v>
       </c>
       <c r="V28">
-        <f>L28-R28</f>
+        <f t="shared" si="2"/>
         <v>-8.2503938809708188E-6</v>
       </c>
       <c r="W28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.435926984791891E-3</v>
       </c>
     </row>
@@ -2378,19 +2384,19 @@
         <v>1.0585233925628601</v>
       </c>
       <c r="T29" t="e">
-        <f>K29-O29</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U29">
-        <f>J29-P29</f>
+        <f t="shared" si="1"/>
         <v>1.7925248343431122E-5</v>
       </c>
       <c r="V29">
-        <f>L29-R29</f>
+        <f t="shared" si="2"/>
         <v>-8.0955849091068899E-6</v>
       </c>
       <c r="W29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.1724265618084928E-4</v>
       </c>
     </row>
@@ -2447,19 +2453,19 @@
         <v>1.0582365466808501</v>
       </c>
       <c r="T30" t="e">
-        <f>K30-O30</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U30">
-        <f>J30-P30</f>
+        <f t="shared" si="1"/>
         <v>1.5663782342301147E-4</v>
       </c>
       <c r="V30">
-        <f>L30-R30</f>
+        <f t="shared" si="2"/>
         <v>-1.7804875341198567E-5</v>
       </c>
       <c r="W30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.2364248472057682E-4</v>
       </c>
     </row>
@@ -2516,19 +2522,19 @@
         <v>1.0474092451916801</v>
       </c>
       <c r="T31" t="e">
-        <f>K31-O31</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U31">
-        <f>J31-P31</f>
+        <f t="shared" si="1"/>
         <v>1.4078958008525433E-3</v>
       </c>
       <c r="V31">
-        <f>L31-R31</f>
+        <f t="shared" si="2"/>
         <v>-7.4800396010488157E-7</v>
       </c>
       <c r="W31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.5621682089017597E-3</v>
       </c>
     </row>
@@ -2585,19 +2591,19 @@
         <v>1.0474656904261199</v>
       </c>
       <c r="T32" t="e">
-        <f>K32-O32</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U32">
-        <f>J32-P32</f>
+        <f t="shared" si="1"/>
         <v>9.6831751156400969E-4</v>
       </c>
       <c r="V32">
-        <f>L32-R32</f>
+        <f t="shared" si="2"/>
         <v>-5.873655513966014E-6</v>
       </c>
       <c r="W32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.0289298386618739E-3</v>
       </c>
     </row>
@@ -2654,19 +2660,19 @@
         <v>1.0474393628534899</v>
       </c>
       <c r="T33" t="e">
-        <f>K33-O33</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U33">
-        <f>J33-P33</f>
+        <f t="shared" si="1"/>
         <v>1.1337072082255872E-3</v>
       </c>
       <c r="V33">
-        <f>L33-R33</f>
+        <f t="shared" si="2"/>
         <v>-5.1235525688753114E-6</v>
       </c>
       <c r="W33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.0297300525037301E-3</v>
       </c>
     </row>
@@ -2723,19 +2729,19 @@
         <v>1.04723672356836</v>
       </c>
       <c r="T34" t="e">
-        <f>K34-O34</f>
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="U34">
-        <f>J34-P34</f>
+        <f t="shared" si="1"/>
         <v>1.6738052498510569E-3</v>
       </c>
       <c r="V34">
-        <f>L34-R34</f>
+        <f t="shared" si="2"/>
         <v>2.3729106013448131E-8</v>
       </c>
       <c r="W34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.3516282249055322E-3</v>
       </c>
     </row>
@@ -2792,19 +2798,19 @@
         <v>1.0288917893998799</v>
       </c>
       <c r="T35" t="e">
-        <f>K35-O35</f>
+        <f t="shared" ref="T35:T62" si="4">K35-O35</f>
         <v>#VALUE!</v>
       </c>
       <c r="U35">
-        <f>J35-P35</f>
+        <f t="shared" ref="U35:U62" si="5">J35-P35</f>
         <v>1.1949165452733723E-3</v>
       </c>
       <c r="V35">
-        <f>L35-R35</f>
+        <f t="shared" ref="V35:V62" si="6">L35-R35</f>
         <v>-1.1274064679600571E-6</v>
       </c>
       <c r="W35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.306384111556703E-4</v>
       </c>
     </row>
@@ -2861,19 +2867,19 @@
         <v>1.02885240401996</v>
       </c>
       <c r="T36" t="e">
-        <f>K36-O36</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U36">
-        <f>J36-P36</f>
+        <f t="shared" si="5"/>
         <v>2.9008528198772865E-3</v>
       </c>
       <c r="V36">
-        <f>L36-R36</f>
+        <f t="shared" si="6"/>
         <v>-1.0892517259275536E-6</v>
       </c>
       <c r="W36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.5342388506195448E-4</v>
       </c>
     </row>
@@ -2930,19 +2936,19 @@
         <v>1.0289408177627799</v>
       </c>
       <c r="T37" t="e">
-        <f>K37-O37</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U37">
-        <f>J37-P37</f>
+        <f t="shared" si="5"/>
         <v>4.1523012090607381E-3</v>
       </c>
       <c r="V37">
-        <f>L37-R37</f>
+        <f t="shared" si="6"/>
         <v>-4.4153808098634784E-6</v>
       </c>
       <c r="W37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.1057911306440182E-3</v>
       </c>
     </row>
@@ -2999,19 +3005,19 @@
         <v>1.02884226326702</v>
       </c>
       <c r="T38" t="e">
-        <f>K38-O38</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U38">
-        <f>J38-P38</f>
+        <f t="shared" si="5"/>
         <v>1.5643319655112009E-4</v>
       </c>
       <c r="V38">
-        <f>L38-R38</f>
+        <f t="shared" si="6"/>
         <v>3.5786120733405369E-9</v>
       </c>
       <c r="W38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-5.2214530914085344E-5</v>
       </c>
     </row>
@@ -3068,19 +3074,19 @@
         <v>0.99999950005706195</v>
       </c>
       <c r="T39" t="e">
-        <f>K39-O39</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U39">
-        <f>J39-P39</f>
+        <f t="shared" si="5"/>
         <v>-7.0287585174355627E-7</v>
       </c>
       <c r="V39">
-        <f>L39-R39</f>
+        <f t="shared" si="6"/>
         <v>-4.9490639620564103E-5</v>
       </c>
       <c r="W39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.3849964616609043E-3</v>
       </c>
     </row>
@@ -3137,19 +3143,19 @@
         <v>0.99999947828584002</v>
       </c>
       <c r="T40" t="e">
-        <f>K40-O40</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U40">
-        <f>J40-P40</f>
+        <f t="shared" si="5"/>
         <v>2.5606221360874315E-4</v>
       </c>
       <c r="V40">
-        <f>L40-R40</f>
+        <f t="shared" si="6"/>
         <v>-5.1645638956099305E-5</v>
       </c>
       <c r="W40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.1988574813054385E-3</v>
       </c>
     </row>
@@ -3206,19 +3212,19 @@
         <v>0.99999945032291404</v>
       </c>
       <c r="T41" t="e">
-        <f>K41-O41</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U41">
-        <f>J41-P41</f>
+        <f t="shared" si="5"/>
         <v>5.4994864325408344E-4</v>
       </c>
       <c r="V41">
-        <f>L41-R41</f>
+        <f t="shared" si="6"/>
         <v>-5.4413503216887982E-5</v>
       </c>
       <c r="W41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.9929358173556011E-3</v>
       </c>
     </row>
@@ -3275,19 +3281,19 @@
         <v>0.99999943210254405</v>
       </c>
       <c r="T42" t="e">
-        <f>K42-O42</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U42">
-        <f>J42-P42</f>
+        <f t="shared" si="5"/>
         <v>7.2768274210943673E-4</v>
       </c>
       <c r="V42">
-        <f>L42-R42</f>
+        <f t="shared" si="6"/>
         <v>-5.6217008226777665E-5</v>
       </c>
       <c r="W42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.8974408829119938E-3</v>
       </c>
     </row>
@@ -3344,19 +3350,19 @@
         <v>1.0287934695107499</v>
       </c>
       <c r="T43" t="e">
-        <f>K43-O43</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U43">
-        <f>J43-P43</f>
+        <f t="shared" si="5"/>
         <v>2.4031432226792049E-3</v>
       </c>
       <c r="V43">
-        <f>L43-R43</f>
+        <f t="shared" si="6"/>
         <v>3.7831371368923783E-9</v>
       </c>
       <c r="W43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5.4696681425125959E-4</v>
       </c>
     </row>
@@ -3413,19 +3419,19 @@
         <v>1.0289274110072999</v>
       </c>
       <c r="T44" t="e">
-        <f>K44-O44</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U44">
-        <f>J44-P44</f>
+        <f t="shared" si="5"/>
         <v>3.8478122252598723E-3</v>
       </c>
       <c r="V44">
-        <f>L44-R44</f>
+        <f t="shared" si="6"/>
         <v>-2.2167893090063728E-6</v>
       </c>
       <c r="W44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.9358684479590167E-4</v>
       </c>
     </row>
@@ -3482,19 +3488,19 @@
         <v>1.0288621309005801</v>
       </c>
       <c r="T45" t="e">
-        <f>K45-O45</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U45">
-        <f>J45-P45</f>
+        <f t="shared" si="5"/>
         <v>3.762820685068391E-3</v>
       </c>
       <c r="V45">
-        <f>L45-R45</f>
+        <f t="shared" si="6"/>
         <v>-4.4303303430304197E-6</v>
       </c>
       <c r="W45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>9.8613765959187916E-4</v>
       </c>
     </row>
@@ -3551,19 +3557,19 @@
         <v>1.0288604694852099</v>
       </c>
       <c r="T46" t="e">
-        <f>K46-O46</f>
+        <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
       <c r="U46">
-        <f>J46-P46</f>
+        <f t="shared" si="5"/>
         <v>3.9332423748703604E-3</v>
       </c>
       <c r="V46">
-        <f>L46-R46</f>
+        <f t="shared" si="6"/>
         <v>-3.3030585819826541E-6</v>
       </c>
       <c r="W46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>9.8440945040501049E-4</v>
       </c>
     </row>
@@ -3620,19 +3626,19 @@
         <v>2.0175346895666801</v>
       </c>
       <c r="T47">
-        <f>K47-O47</f>
+        <f t="shared" si="4"/>
         <v>-9.0529799155305568E-3</v>
       </c>
       <c r="U47">
-        <f>J47-P47</f>
+        <f t="shared" si="5"/>
         <v>6.4968343910081217E-3</v>
       </c>
       <c r="V47">
-        <f>L47-R47</f>
+        <f t="shared" si="6"/>
         <v>-1.7439217287300579E-3</v>
       </c>
       <c r="W47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4.0093979865707396E-4</v>
       </c>
     </row>
@@ -3689,19 +3695,19 @@
         <v>1.8723355117888201</v>
       </c>
       <c r="T48">
-        <f>K48-O48</f>
+        <f t="shared" si="4"/>
         <v>-8.839232938949948E-3</v>
       </c>
       <c r="U48">
-        <f>J48-P48</f>
+        <f t="shared" si="5"/>
         <v>9.2950685608315098E-3</v>
       </c>
       <c r="V48">
-        <f>L48-R48</f>
+        <f t="shared" si="6"/>
         <v>-7.5328216083114796E-4</v>
       </c>
       <c r="W48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4.5633283061263796E-4</v>
       </c>
     </row>
@@ -3758,19 +3764,19 @@
         <v>1.74867776453277</v>
       </c>
       <c r="T49">
-        <f>K49-O49</f>
+        <f t="shared" si="4"/>
         <v>-9.1404240267003445E-3</v>
       </c>
       <c r="U49">
-        <f>J49-P49</f>
+        <f t="shared" si="5"/>
         <v>2.6769890178215405E-3</v>
       </c>
       <c r="V49">
-        <f>L49-R49</f>
+        <f t="shared" si="6"/>
         <v>-2.0545704399999032E-4</v>
       </c>
       <c r="W49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.0472490781499033E-4</v>
       </c>
     </row>
@@ -3827,19 +3833,19 @@
         <v>1.64765815247592</v>
       </c>
       <c r="T50">
-        <f>K50-O50</f>
+        <f t="shared" si="4"/>
         <v>-7.8973963160713367E-3</v>
       </c>
       <c r="U50">
-        <f>J50-P50</f>
+        <f t="shared" si="5"/>
         <v>1.0650506363980128E-2</v>
       </c>
       <c r="V50">
-        <f>L50-R50</f>
+        <f t="shared" si="6"/>
         <v>-1.6728142534589985E-3</v>
       </c>
       <c r="W50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.9501457760705563E-4</v>
       </c>
     </row>
@@ -3868,7 +3874,7 @@
       <c r="H51">
         <v>1.000219166149563E-2</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="1">
         <v>4.2129653443995503</v>
       </c>
       <c r="J51">
@@ -3896,19 +3902,19 @@
         <v>1.7997402799403901</v>
       </c>
       <c r="T51">
-        <f>K51-O51</f>
+        <f t="shared" si="4"/>
         <v>-4.3195555986912382E-3</v>
       </c>
       <c r="U51">
-        <f>J51-P51</f>
+        <f t="shared" si="5"/>
         <v>-3.3880870873588265E-3</v>
       </c>
       <c r="V51">
-        <f>L51-R51</f>
+        <f t="shared" si="6"/>
         <v>-3.063239888767999E-3</v>
       </c>
       <c r="W51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4.8713833656788275E-5</v>
       </c>
     </row>
@@ -3937,7 +3943,7 @@
       <c r="H52">
         <v>1.000219166149563E-2</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="1">
         <v>4.3951716448785998</v>
       </c>
       <c r="J52">
@@ -3965,19 +3971,19 @@
         <v>1.81459530536096</v>
       </c>
       <c r="T52">
-        <f>K52-O52</f>
+        <f t="shared" si="4"/>
         <v>-3.0033824977699908E-3</v>
       </c>
       <c r="U52">
-        <f>J52-P52</f>
+        <f t="shared" si="5"/>
         <v>8.1637229684048407E-3</v>
       </c>
       <c r="V52">
-        <f>L52-R52</f>
+        <f t="shared" si="6"/>
         <v>-1.1239566327070349E-3</v>
       </c>
       <c r="W52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>-1.4052684876975086E-5</v>
       </c>
     </row>
@@ -4006,7 +4012,7 @@
       <c r="H53">
         <v>1.000219166149563E-2</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="1">
         <v>4.4935715744873796</v>
       </c>
       <c r="J53">
@@ -4034,19 +4040,19 @@
         <v>1.83215851072586</v>
       </c>
       <c r="T53">
-        <f>K53-O53</f>
+        <f t="shared" si="4"/>
         <v>-1.6635277014191985E-3</v>
       </c>
       <c r="U53">
-        <f>J53-P53</f>
+        <f t="shared" si="5"/>
         <v>1.5924194574239436E-3</v>
       </c>
       <c r="V53">
-        <f>L53-R53</f>
+        <f t="shared" si="6"/>
         <v>-1.5468665135398574E-4</v>
       </c>
       <c r="W53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1.4916942405740485E-5</v>
       </c>
     </row>
@@ -4075,7 +4081,7 @@
       <c r="H54">
         <v>1.000219166149563E-2</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="1">
         <v>4.7094791191536398</v>
       </c>
       <c r="J54">
@@ -4103,19 +4109,19 @@
         <v>1.64302045518508</v>
       </c>
       <c r="T54">
-        <f>K54-O54</f>
+        <f t="shared" si="4"/>
         <v>-5.9281083531192991E-3</v>
       </c>
       <c r="U54">
-        <f>J54-P54</f>
+        <f t="shared" si="5"/>
         <v>-2.6955998769579992E-3</v>
       </c>
       <c r="V54">
-        <f>L54-R54</f>
+        <f t="shared" si="6"/>
         <v>-2.2380846393939002E-3</v>
       </c>
       <c r="W54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2.9813980124693273E-5</v>
       </c>
     </row>
@@ -4144,7 +4150,7 @@
       <c r="H55">
         <v>1.000953753752501E-2</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="1">
         <v>9.0995914438217707</v>
       </c>
       <c r="J55">
@@ -4172,19 +4178,19 @@
         <v>1.77410774900271</v>
       </c>
       <c r="T55">
-        <f>K55-O55</f>
+        <f t="shared" si="4"/>
         <v>-3.4135875109164715E-3</v>
       </c>
       <c r="U55">
-        <f>J55-P55</f>
+        <f t="shared" si="5"/>
         <v>-1.5756639768227387E-2</v>
       </c>
       <c r="V55">
-        <f>L55-R55</f>
+        <f t="shared" si="6"/>
         <v>-1.5434706826029654E-3</v>
       </c>
       <c r="W55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.5360087715036226E-5</v>
       </c>
     </row>
@@ -4213,7 +4219,7 @@
       <c r="H56">
         <v>1.000953753752501E-2</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="1">
         <v>9.4952496649515297</v>
       </c>
       <c r="J56">
@@ -4241,19 +4247,19 @@
         <v>1.7915034598559501</v>
       </c>
       <c r="T56">
-        <f>K56-O56</f>
+        <f t="shared" si="4"/>
         <v>-2.8877049868061277E-3</v>
       </c>
       <c r="U56">
-        <f>J56-P56</f>
+        <f t="shared" si="5"/>
         <v>-1.1602287524823396E-2</v>
       </c>
       <c r="V56">
-        <f>L56-R56</f>
+        <f t="shared" si="6"/>
         <v>-3.5363695232730752E-3</v>
       </c>
       <c r="W56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5.6953772023304872E-5</v>
       </c>
     </row>
@@ -4282,7 +4288,7 @@
       <c r="H57">
         <v>1.000953753752501E-2</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="1">
         <v>9.7003630222173491</v>
       </c>
       <c r="J57">
@@ -4310,19 +4316,19 @@
         <v>1.79469595288914</v>
       </c>
       <c r="T57">
-        <f>K57-O57</f>
+        <f t="shared" si="4"/>
         <v>-2.5278146626259712E-3</v>
       </c>
       <c r="U57">
-        <f>J57-P57</f>
+        <f t="shared" si="5"/>
         <v>-1.512212360951537E-2</v>
       </c>
       <c r="V57">
-        <f>L57-R57</f>
+        <f t="shared" si="6"/>
         <v>-2.4130331421370332E-3</v>
       </c>
       <c r="W57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.346124600143833E-5</v>
       </c>
     </row>
@@ -4351,7 +4357,7 @@
       <c r="H58">
         <v>1.000953753752501E-2</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="1">
         <v>9.8260517694073304</v>
       </c>
       <c r="J58">
@@ -4379,19 +4385,19 @@
         <v>1.7994135989231299</v>
       </c>
       <c r="T58">
-        <f>K58-O58</f>
+        <f t="shared" si="4"/>
         <v>-2.4030660486555888E-3</v>
       </c>
       <c r="U58">
-        <f>J58-P58</f>
+        <f t="shared" si="5"/>
         <v>-1.8680183435265008E-2</v>
       </c>
       <c r="V58">
-        <f>L58-R58</f>
+        <f t="shared" si="6"/>
         <v>-2.0472359652399241E-3</v>
       </c>
       <c r="W58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.6947012196914031E-5</v>
       </c>
     </row>
@@ -4420,7 +4426,7 @@
       <c r="H59">
         <v>1.002948897160582E-2</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="1">
         <v>15.4099635909299</v>
       </c>
       <c r="J59">
@@ -4448,19 +4454,19 @@
         <v>1.7006767003999199</v>
       </c>
       <c r="T59">
-        <f>K59-O59</f>
+        <f t="shared" si="4"/>
         <v>-1.5262447654187383E-3</v>
       </c>
       <c r="U59">
-        <f>J59-P59</f>
+        <f t="shared" si="5"/>
         <v>-9.2585053411369245E-3</v>
       </c>
       <c r="V59">
-        <f>L59-R59</f>
+        <f t="shared" si="6"/>
         <v>-8.9174093982391511E-4</v>
       </c>
       <c r="W59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7.5608433123902641E-5</v>
       </c>
     </row>
@@ -4489,7 +4495,7 @@
       <c r="H60">
         <v>1.002948897160582E-2</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="1">
         <v>16.069345158962999</v>
       </c>
       <c r="J60">
@@ -4517,19 +4523,19 @@
         <v>1.7018645352745601</v>
       </c>
       <c r="T60">
-        <f>K60-O60</f>
+        <f t="shared" si="4"/>
         <v>-1.1396316393952333E-3</v>
       </c>
       <c r="U60">
-        <f>J60-P60</f>
+        <f t="shared" si="5"/>
         <v>-1.0636735350331605E-2</v>
       </c>
       <c r="V60">
-        <f>L60-R60</f>
+        <f t="shared" si="6"/>
         <v>-2.5188049751421193E-3</v>
       </c>
       <c r="W60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.6086715093691701E-5</v>
       </c>
     </row>
@@ -4558,7 +4564,7 @@
       <c r="H61">
         <v>1.002948897160582E-2</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="1">
         <v>16.403879681171301</v>
       </c>
       <c r="J61">
@@ -4586,19 +4592,19 @@
         <v>1.7057671352095101</v>
       </c>
       <c r="T61">
-        <f>K61-O61</f>
+        <f t="shared" si="4"/>
         <v>-1.0458816609055788E-3</v>
       </c>
       <c r="U61">
-        <f>J61-P61</f>
+        <f t="shared" si="5"/>
         <v>-1.036551770377514E-2</v>
       </c>
       <c r="V61">
-        <f>L61-R61</f>
+        <f t="shared" si="6"/>
         <v>-3.0135630134251468E-3</v>
       </c>
       <c r="W61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8.2521353398007369E-5</v>
       </c>
     </row>
@@ -4627,7 +4633,7 @@
       <c r="H62">
         <v>1.002948897160582E-2</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="1">
         <v>16.603264930804301</v>
       </c>
       <c r="J62">
@@ -4655,19 +4661,19 @@
         <v>1.70406690405371</v>
       </c>
       <c r="T62">
-        <f>K62-O62</f>
+        <f t="shared" si="4"/>
         <v>-8.4576539343395041E-4</v>
       </c>
       <c r="U62">
-        <f>J62-P62</f>
+        <f t="shared" si="5"/>
         <v>-7.575916484853451E-3</v>
       </c>
       <c r="V62">
-        <f>L62-R62</f>
+        <f t="shared" si="6"/>
         <v>-2.3474301545989285E-3</v>
       </c>
       <c r="W62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6.0645033899187073E-5</v>
       </c>
     </row>
